--- a/services_forms/050_it_service_request_form--services_forms.xlsx
+++ b/services_forms/050_it_service_request_form--services_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -918,8 +918,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -947,12 +947,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -964,12 +964,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -981,12 +981,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -998,12 +998,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1015,12 +1015,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_true,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': True, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_false,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': False, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'hardware',_'value':_'hardware'}</t>
+          <t>hardware</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Hardware', 'value': 'hardware'}</t>
+          <t>Hardware</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'software',_'value':_'software'}</t>
+          <t>software</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Software', 'value': 'software'}</t>
+          <t>Software</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'network',_'value':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Network', 'value': 'network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'network_and_hardware',_'value':_'hardware_and_network'}</t>
+          <t>network_and_hardware</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Network and Hardware', 'value': 'hardware_and_network'}</t>
+          <t>Network and Hardware</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Jimmy', 'value': 'jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'sarah',_'value':_'sarah'}</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Sarah', 'value': 'sarah'}</t>
+          <t>Sarah</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'jimmy',_'value':_'jimmy'}</t>
+          <t>jimmy</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Jimmy', 'value': 'jimmy'}</t>
+          <t>Jimmy</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'sarah',_'value':_'sarah'}</t>
+          <t>sarah</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Sarah', 'value': 'sarah'}</t>
+          <t>Sarah</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'john',_'value':_'john'}</t>
+          <t>john</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'John', 'value': 'john'}</t>
+          <t>John</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'low',_'value':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Low', 'value': 'low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'medium',_'value':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Medium', 'value': 'medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'high',_'value':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'High', 'value': 'high'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
